--- a/report/downloads/reports/网点变化对比报告_20260824_vs_20260831.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260824_vs_20260831.xlsx
@@ -11924,7 +11924,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>南京利之星汽车销售服务有限公司河西分公司</t>
+          <t>南京利之星汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -11939,12 +11939,12 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>鼓楼区汉中门大街309号B栋一层</t>
+          <t>栖霞区仙尧路9号</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>连续在档 17 期</t>
+          <t>连续在档 17 期；本期存在高相似店名「福州利之星汽车销售服务有限公司」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>南京利之星汽车销售服务有限公司</t>
+          <t>南京利之星汽车销售服务有限公司河西分公司</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -11971,12 +11971,12 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>栖霞区仙尧路9号</t>
+          <t>鼓楼区汉中门大街309号B栋一层</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>连续在档 17 期；本期存在高相似店名「福州利之星汽车销售服务有限公司」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 17 期</t>
         </is>
       </c>
     </row>
@@ -12485,22 +12485,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 襄阳光彩</t>
+          <t>小米汽车浙江省衢州市龙游县龙游银泰</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 襄阳光彩</t>
+          <t>小米汽车浙江省衢州市龙游县龙游银泰</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12510,29 +12510,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>湖北省襄阳市襄州区钻石大道28号 → 襄州区钻石大道与西湾路交叉口东北120米</t>
+          <t>龙游县龙洲街道兴龙南路45号 → 浙江省衢州市龙游县兴龙南路45号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车潍坊渤海路销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车潍坊渤海路销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12542,29 +12542,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>日新东路259号 西山区 650103 → 日新东路259号 西山区 650228</t>
+          <t>山东省潍坊市寒亭区通亭街6369号 → 山东省潍坊市寒亭区开元街道通亭街6369号202号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省泰安市岱岳区泰山国际汽车城</t>
+          <t>蔚来空间 | 珠海环宇城</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省泰安市岱岳区泰山国际汽车城</t>
+          <t>蔚来空间 | 珠海环宇城</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12574,7 +12574,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>山东省泰安市泰山国际汽车城山东临工（泰东路） → 秦东路202号</t>
+          <t>广东省珠海市香洲区前河北路 96 号珠海环宇城L1-115 → 广东省珠海市香洲区前河北路 96 号珠海环宇城L1-115、LL6</t>
         </is>
       </c>
     </row>
@@ -12586,17 +12586,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州开发区销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州开发区销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12606,29 +12606,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市开发区石港路71号 → 河北省沧州市开发区黄河路与石岗路交叉口路北</t>
+          <t>安徽省安庆市英德利国际汽车城福旺路 → 安庆市英德利国际汽车城松祥路与福旺路交叉口北60米</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海环宇城</t>
+          <t>小鹏汽车沧州开发区销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海环宇城</t>
+          <t>小鹏汽车沧州开发区销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12638,29 +12638,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广东省珠海市香洲区前河北路 96 号珠海环宇城L1-115 → 广东省珠海市香洲区前河北路 96 号珠海环宇城L1-115、LL6</t>
+          <t>河北省沧州市开发区石港路71号 → 河北省沧州市开发区黄河路与石岗路交叉口路北</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省恩施市恩施和润城</t>
+          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省恩施市恩施和润城</t>
+          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12670,29 +12670,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>湖北省恩施土家族苗族自治州恩施市和润城A馆中庭 → 湖北省恩施土家族苗族自治州恩施市和润城B馆中庭</t>
+          <t>山东省东营市垦利区董集镇北二路14号 → 山东省东营市垦利区董集镇北二路5号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12702,29 +12702,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧） → 汕头市龙湖区南山路居委长平路与泰山路交界东北侧“车展”西北角20号</t>
+          <t>日新东路259号 西山区 650103 → 日新东路259号 西山区 650228</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Bentley Xiamen</t>
+          <t>小鹏汽车重庆金菱车世界销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Bentley Xiamen</t>
+          <t>小鹏汽车重庆金菱车世界销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12734,29 +12734,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Room 107 113, 1/F, No.88  Shuangshi West Road → Unit 10, 1F, Podium Block Guojin Plaza, No. 506-508</t>
+          <t>重庆经开区白鹤路工业园区1号 → 重庆市南岸区经开区白鹤路工业园1号（附9号）</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小米汽车湖北省恩施市恩施和润城</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小米汽车湖北省恩施市恩施和润城</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12766,29 +12766,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>安徽省安庆市英德利国际汽车城福旺路 → 安庆市英德利国际汽车城松祥路与福旺路交叉口北60米</t>
+          <t>湖北省恩施土家族苗族自治州恩施市和润城A馆中庭 → 湖北省恩施土家族苗族自治州恩施市和润城B馆中庭</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊渤海路销售服务中心</t>
+          <t>上汽奥迪天津奥兴用户中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊渤海路销售服务中心</t>
+          <t>上汽奥迪天津奥兴用户中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12798,29 +12798,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市寒亭区通亭街6369号 → 山东省潍坊市寒亭区开元街道通亭街6369号202号</t>
+          <t>双街镇京津公路东侧双江道南庞大汽贸园内21号 → 天津市双街镇京津公路双江道南庞大汽贸园21号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆金菱车世界销售服务中心</t>
+          <t>蔚来体验中心 | 襄阳光彩</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆金菱车世界销售服务中心</t>
+          <t>蔚来体验中心 | 襄阳光彩</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12830,7 +12830,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>重庆经开区白鹤路工业园区1号 → 重庆市南岸区经开区白鹤路工业园1号（附9号）</t>
+          <t>湖北省襄阳市襄州区钻石大道28号 → 襄州区钻石大道与西湾路交叉口东北120米</t>
         </is>
       </c>
     </row>
@@ -12842,17 +12842,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12862,7 +12862,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>山东省东营市垦利区董集镇北二路14号 → 山东省东营市垦利区董集镇北二路5号</t>
+          <t>汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧） → 汕头市龙湖区南山路居委长平路与泰山路交界东北侧“车展”西北角20号</t>
         </is>
       </c>
     </row>
@@ -12874,17 +12874,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省衢州市龙游县龙游银泰</t>
+          <t>小米汽车山东省泰安市岱岳区泰山国际汽车城</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省衢州市龙游县龙游银泰</t>
+          <t>小米汽车山东省泰安市岱岳区泰山国际汽车城</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12894,29 +12894,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>龙游县龙洲街道兴龙南路45号 → 浙江省衢州市龙游县兴龙南路45号</t>
+          <t>山东省泰安市泰山国际汽车城山东临工（泰东路） → 秦东路202号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪天津奥兴用户中心</t>
+          <t>Bentley Xiamen</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪天津奥兴用户中心</t>
+          <t>Bentley Xiamen</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>双街镇京津公路东侧双江道南庞大汽贸园内21号 → 天津市双街镇京津公路双江道南庞大汽贸园21号</t>
+          <t>Room 107 113, 1/F, No.88  Shuangshi West Road → Unit 10, 1F, Podium Block Guojin Plaza, No. 506-508</t>
         </is>
       </c>
     </row>
@@ -12997,22 +12997,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>马鞍山雨山万达广场</t>
+          <t>华为智能生活馆•烟台龙口保利</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>马鞍山雨山万达广场城市展厅1号门</t>
+          <t>华为授权体验店（龙口保利广场）</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13029,22 +13029,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•烟台龙口保利</t>
+          <t>马鞍山雨山万达广场</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（龙口保利广场）</t>
+          <t>马鞍山雨山万达广场城市展厅1号门</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13098,17 +13098,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十路</t>
+          <t>小米汽车四川省绵阳市涪城区万达广场</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十东路</t>
+          <t>小米汽车四川省绵阳市涪城区绵阳涪城万达</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 97%</t>
+          <t>店名相似度 83%</t>
         </is>
       </c>
     </row>
@@ -13130,17 +13130,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区万达广场</t>
+          <t>小米汽车山东省济南市历城区经十路</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵阳涪城万达</t>
+          <t>小米汽车山东省济南市历城区经十东路</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13150,7 +13150,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 83%</t>
+          <t>店名相似度 97%</t>
         </is>
       </c>
     </row>
